--- a/03_analysis_input/adults_adolescents_stratification_info.xlsx
+++ b/03_analysis_input/adults_adolescents_stratification_info.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F616"/>
+  <dimension ref="A1:F615"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,7 +394,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -403,11 +403,16 @@
         </is>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -419,7 +424,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>20008</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -428,11 +433,16 @@
         </is>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -444,7 +454,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -453,11 +463,11 @@
         </is>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -474,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>20012</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -483,11 +493,11 @@
         </is>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -504,7 +514,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20009</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -513,7 +523,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -534,7 +544,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -543,11 +553,11 @@
         </is>
       </c>
       <c r="D7">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -564,7 +574,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -573,11 +583,11 @@
         </is>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -594,7 +604,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20014</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -603,11 +613,11 @@
         </is>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -624,7 +634,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -633,11 +643,11 @@
         </is>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -654,7 +664,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -663,7 +673,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -684,7 +694,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -693,11 +703,11 @@
         </is>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -714,7 +724,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -723,7 +733,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -744,7 +754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -753,11 +763,11 @@
         </is>
       </c>
       <c r="D14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -774,7 +784,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20021</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -783,11 +793,11 @@
         </is>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -804,7 +814,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -813,16 +823,16 @@
         </is>
       </c>
       <c r="D16">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -834,7 +844,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>20025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -843,7 +853,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -864,7 +874,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -873,7 +883,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -882,7 +892,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -894,7 +904,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -903,7 +913,7 @@
         </is>
       </c>
       <c r="D19">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -924,7 +934,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -933,16 +943,11 @@
         </is>
       </c>
       <c r="D20">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>patient</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -954,7 +959,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20028</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -963,7 +968,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -984,7 +989,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20029</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -993,11 +998,16 @@
         </is>
       </c>
       <c r="D22">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1019,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1018,11 +1028,11 @@
         </is>
       </c>
       <c r="D23">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1039,7 +1049,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1048,11 +1058,11 @@
         </is>
       </c>
       <c r="D24">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1069,7 +1079,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1078,16 +1088,16 @@
         </is>
       </c>
       <c r="D25">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1109,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1108,7 +1118,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1129,7 +1139,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20038</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1138,7 +1148,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1147,7 +1157,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1169,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20041</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1168,16 +1178,16 @@
         </is>
       </c>
       <c r="D28">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1199,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20038</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1198,7 +1208,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1207,7 +1217,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1229,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>20043</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1228,7 +1238,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1237,7 +1247,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1259,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1258,7 +1268,7 @@
         </is>
       </c>
       <c r="D31">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1279,7 +1289,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>20045</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1288,11 +1298,11 @@
         </is>
       </c>
       <c r="D32">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1309,7 +1319,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1318,7 +1328,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1339,7 +1349,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20045</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1348,7 +1358,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1369,7 +1379,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20046</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,7 +1388,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1387,7 +1397,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1409,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>20052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1408,16 +1418,16 @@
         </is>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1439,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>20053</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1438,16 +1448,11 @@
         </is>
       </c>
       <c r="D37">
-        <v>49</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>42</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1464,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1468,7 +1473,7 @@
         </is>
       </c>
       <c r="D38">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1498,11 +1503,16 @@
         </is>
       </c>
       <c r="D39">
-        <v>42</v>
+        <v>39</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1524,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>20058</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1523,7 +1533,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>20059</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1553,7 +1563,7 @@
         </is>
       </c>
       <c r="D41">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20058</t>
+          <t>20060</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1583,7 +1593,7 @@
         </is>
       </c>
       <c r="D42">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1592,7 +1602,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1614,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1613,7 +1623,7 @@
         </is>
       </c>
       <c r="D43">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1622,7 +1632,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1644,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1643,7 +1653,7 @@
         </is>
       </c>
       <c r="D44">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1664,7 +1674,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1673,11 +1683,11 @@
         </is>
       </c>
       <c r="D45">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1694,7 +1704,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1703,16 +1713,16 @@
         </is>
       </c>
       <c r="D46">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1734,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1733,11 +1743,11 @@
         </is>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1754,7 +1764,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1767,7 +1777,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1784,7 +1794,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20065</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1793,11 +1803,11 @@
         </is>
       </c>
       <c r="D49">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1814,7 +1824,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1823,11 +1833,11 @@
         </is>
       </c>
       <c r="D50">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1844,7 +1854,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1853,11 +1863,11 @@
         </is>
       </c>
       <c r="D51">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1874,7 +1884,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1883,16 +1893,11 @@
         </is>
       </c>
       <c r="D52">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>male</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1909,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1913,16 +1918,11 @@
         </is>
       </c>
       <c r="D53">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>female</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>HC</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="D54">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1968,11 +1968,11 @@
         </is>
       </c>
       <c r="D55">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2068,11 +2068,11 @@
         </is>
       </c>
       <c r="D59">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2093,11 +2093,11 @@
         </is>
       </c>
       <c r="D60">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>20084</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2118,11 +2118,11 @@
         </is>
       </c>
       <c r="D61">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>70083</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9284,11 +9284,11 @@
         </is>
       </c>
       <c r="D349">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>70095</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -9309,7 +9309,7 @@
         </is>
       </c>
       <c r="D350">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>70095</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D351">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>70096</t>
+          <t>70097</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9359,11 +9359,11 @@
         </is>
       </c>
       <c r="D352">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>70097</t>
+          <t>70101</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="D353">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>70101</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9413,7 +9413,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9425,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>70103</t>
+          <t>70111</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -9436,11 +9436,6 @@
       <c r="D355">
         <v>28</v>
       </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -9450,7 +9445,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>70111</t>
+          <t>70126</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -9461,6 +9456,11 @@
       <c r="D356">
         <v>28</v>
       </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>70126</t>
+          <t>70129</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="D357">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>70130</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>70130</t>
+          <t>70131</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="D359">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>70131</t>
+          <t>70133</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -9554,7 +9554,7 @@
         </is>
       </c>
       <c r="D360">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>70133</t>
+          <t>70134</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -9579,11 +9579,11 @@
         </is>
       </c>
       <c r="D361">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>70134</t>
+          <t>70137</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -9604,11 +9604,11 @@
         </is>
       </c>
       <c r="D362">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>70137</t>
+          <t>70139</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -9629,11 +9629,11 @@
         </is>
       </c>
       <c r="D363">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>70139</t>
+          <t>70149</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="D364">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>70149</t>
+          <t>70152</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -9679,11 +9679,11 @@
         </is>
       </c>
       <c r="D365">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>70152</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -9703,12 +9703,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="D366">
-        <v>27</v>
-      </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9717,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>70153</t>
+          <t>70164</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -9728,9 +9725,12 @@
           <t>7</t>
         </is>
       </c>
+      <c r="D367">
+        <v>27</v>
+      </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>70164</t>
+          <t>70167</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -9751,11 +9751,11 @@
         </is>
       </c>
       <c r="D368">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>70167</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -9776,11 +9776,11 @@
         </is>
       </c>
       <c r="D369">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>70190</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="D370">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>70190</t>
+          <t>70191</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -9826,12 +9826,7 @@
         </is>
       </c>
       <c r="D371">
-        <v>28</v>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>25</v>
       </c>
     </row>
     <row r="372">
@@ -9842,7 +9837,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>70191</t>
+          <t>70192</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -9851,7 +9846,12 @@
         </is>
       </c>
       <c r="D372">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>70192</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="D373">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>70207</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -9896,11 +9896,11 @@
         </is>
       </c>
       <c r="D374">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>70207</t>
+          <t>70211</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -9921,11 +9921,11 @@
         </is>
       </c>
       <c r="D375">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -9937,7 +9937,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>70211</t>
+          <t>70212</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -9946,11 +9946,11 @@
         </is>
       </c>
       <c r="D376">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>70212</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="D377">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>70215</t>
+          <t>70216</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="D378">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>70216</t>
+          <t>70217</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>70217</t>
+          <t>70218</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="D380">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>70225</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10071,7 +10071,7 @@
         </is>
       </c>
       <c r="D381">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>70225</t>
+          <t>70231</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="D382">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>70231</t>
+          <t>70235</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="D383">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>70235</t>
+          <t>70236</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10146,11 +10146,11 @@
         </is>
       </c>
       <c r="D384">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>70236</t>
+          <t>70237</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10171,11 +10171,11 @@
         </is>
       </c>
       <c r="D385">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>70237</t>
+          <t>70299</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -10196,11 +10196,11 @@
         </is>
       </c>
       <c r="D386">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -10212,20 +10212,25 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>70299</t>
+          <t>80002</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D387">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10242,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>80002</t>
+          <t>80003</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -10246,11 +10251,11 @@
         </is>
       </c>
       <c r="D388">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -10267,7 +10272,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>80003</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10276,11 +10281,11 @@
         </is>
       </c>
       <c r="D389">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -10297,7 +10302,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>80005</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10306,7 +10311,7 @@
         </is>
       </c>
       <c r="D390">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -10327,7 +10332,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10336,11 +10341,11 @@
         </is>
       </c>
       <c r="D391">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -10357,7 +10362,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>80006</t>
+          <t>80007</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -10366,11 +10371,11 @@
         </is>
       </c>
       <c r="D392">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -10387,7 +10392,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>80007</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -10396,7 +10401,7 @@
         </is>
       </c>
       <c r="D393">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -10417,7 +10422,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -10426,7 +10431,7 @@
         </is>
       </c>
       <c r="D394">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -10447,7 +10452,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -10456,11 +10461,11 @@
         </is>
       </c>
       <c r="D395">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -10477,7 +10482,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>80012</t>
+          <t>80013</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -10486,11 +10491,11 @@
         </is>
       </c>
       <c r="D396">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -10507,7 +10512,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -10516,7 +10521,7 @@
         </is>
       </c>
       <c r="D397">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -10537,7 +10542,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>80015</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -10546,11 +10551,11 @@
         </is>
       </c>
       <c r="D398">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -10567,7 +10572,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>80015</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -10576,11 +10581,11 @@
         </is>
       </c>
       <c r="D399">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -10597,7 +10602,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -10606,7 +10611,7 @@
         </is>
       </c>
       <c r="D400">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -10627,7 +10632,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>80017</t>
+          <t>80019</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -10657,7 +10662,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>80019</t>
+          <t>80020</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -10666,7 +10671,7 @@
         </is>
       </c>
       <c r="D402">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -10687,7 +10692,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>80020</t>
+          <t>80021</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -10696,7 +10701,7 @@
         </is>
       </c>
       <c r="D403">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -10717,7 +10722,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>80021</t>
+          <t>80022</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -10726,7 +10731,7 @@
         </is>
       </c>
       <c r="D404">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -10747,7 +10752,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>80022</t>
+          <t>80023</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -10777,7 +10782,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>80023</t>
+          <t>80024</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -10786,7 +10791,7 @@
         </is>
       </c>
       <c r="D406">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -10795,7 +10800,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10812,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>80025</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -10816,7 +10821,7 @@
         </is>
       </c>
       <c r="D407">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -10837,7 +10842,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>80026</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -10846,7 +10851,7 @@
         </is>
       </c>
       <c r="D408">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -10867,7 +10872,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>80026</t>
+          <t>80027</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -10876,11 +10881,11 @@
         </is>
       </c>
       <c r="D409">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -10897,7 +10902,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>80027</t>
+          <t>80028</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -10906,11 +10911,11 @@
         </is>
       </c>
       <c r="D410">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -10927,7 +10932,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>80028</t>
+          <t>80029</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -10936,7 +10941,7 @@
         </is>
       </c>
       <c r="D411">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -10957,7 +10962,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>80029</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -10966,11 +10971,11 @@
         </is>
       </c>
       <c r="D412">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -10987,7 +10992,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>80032</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -10996,11 +11001,11 @@
         </is>
       </c>
       <c r="D413">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -11017,7 +11022,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>80032</t>
+          <t>80033</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11026,7 +11031,7 @@
         </is>
       </c>
       <c r="D414">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -11047,7 +11052,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>80033</t>
+          <t>80034</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -11056,7 +11061,7 @@
         </is>
       </c>
       <c r="D415">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -11065,7 +11070,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11082,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>80034</t>
+          <t>80035</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -11086,11 +11091,11 @@
         </is>
       </c>
       <c r="D416">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -11107,7 +11112,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>80035</t>
+          <t>80038</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11116,11 +11121,11 @@
         </is>
       </c>
       <c r="D417">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -11137,7 +11142,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>80038</t>
+          <t>80039</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11146,11 +11151,11 @@
         </is>
       </c>
       <c r="D418">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -11167,7 +11172,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>80039</t>
+          <t>80040</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -11176,7 +11181,7 @@
         </is>
       </c>
       <c r="D419">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -11185,7 +11190,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11202,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>80041</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -11206,7 +11211,7 @@
         </is>
       </c>
       <c r="D420">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -11215,7 +11220,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11232,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>80041</t>
+          <t>80043</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11236,7 +11241,7 @@
         </is>
       </c>
       <c r="D421">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -11257,7 +11262,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>80043</t>
+          <t>80044</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11266,16 +11271,16 @@
         </is>
       </c>
       <c r="D422">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11287,7 +11292,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>80044</t>
+          <t>80045</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11296,16 +11301,16 @@
         </is>
       </c>
       <c r="D423">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11317,7 +11322,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>80045</t>
+          <t>80046</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11326,7 +11331,7 @@
         </is>
       </c>
       <c r="D424">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -11347,7 +11352,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>80046</t>
+          <t>80048</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -11356,7 +11361,7 @@
         </is>
       </c>
       <c r="D425">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -11365,7 +11370,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11382,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>80048</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -11386,7 +11391,7 @@
         </is>
       </c>
       <c r="D426">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -11395,7 +11400,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11407,7 +11412,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>80050</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -11415,12 +11420,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="D427">
-        <v>26</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>male</t>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11432,12 +11434,25 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>80050</t>
+          <t>80052</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="D428">
+        <v>24</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11449,7 +11464,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>80052</t>
+          <t>80054</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -11458,11 +11473,16 @@
         </is>
       </c>
       <c r="D429">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11494,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>80054</t>
+          <t>80055</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -11483,11 +11503,16 @@
         </is>
       </c>
       <c r="D430">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11524,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>80055</t>
+          <t>80056</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -11508,11 +11533,11 @@
         </is>
       </c>
       <c r="D431">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11549,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>80056</t>
+          <t>80057</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -11533,11 +11558,16 @@
         </is>
       </c>
       <c r="D432">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11579,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>80058</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -11558,7 +11588,7 @@
         </is>
       </c>
       <c r="D433">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -11574,7 +11604,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>80058</t>
+          <t>80059</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -11583,11 +11613,16 @@
         </is>
       </c>
       <c r="D434">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11634,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>80059</t>
+          <t>80060</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -11608,11 +11643,16 @@
         </is>
       </c>
       <c r="D435">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11664,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>80060</t>
+          <t>80062</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -11633,7 +11673,7 @@
         </is>
       </c>
       <c r="D436">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -11649,7 +11689,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>80062</t>
+          <t>80063</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -11658,11 +11698,16 @@
         </is>
       </c>
       <c r="D437">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11719,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>80063</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -11683,11 +11728,16 @@
         </is>
       </c>
       <c r="D438">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11749,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>80064</t>
+          <t>80065</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -11708,11 +11758,16 @@
         </is>
       </c>
       <c r="D439">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11779,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>80065</t>
+          <t>80067</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -11733,11 +11788,16 @@
         </is>
       </c>
       <c r="D440">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -11749,7 +11809,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>80067</t>
+          <t>80068</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -11758,11 +11818,11 @@
         </is>
       </c>
       <c r="D441">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11834,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>80068</t>
+          <t>80069</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -11783,11 +11843,16 @@
         </is>
       </c>
       <c r="D442">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11864,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>80069</t>
+          <t>80070</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -11808,7 +11873,7 @@
         </is>
       </c>
       <c r="D443">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -11824,7 +11889,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>80070</t>
+          <t>80071</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -11833,7 +11898,7 @@
         </is>
       </c>
       <c r="D444">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -11849,7 +11914,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>80072</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -11858,7 +11923,7 @@
         </is>
       </c>
       <c r="D445">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -11874,7 +11939,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>80073</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -11883,7 +11948,7 @@
         </is>
       </c>
       <c r="D446">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -11899,7 +11964,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>80073</t>
+          <t>80074</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -11908,7 +11973,7 @@
         </is>
       </c>
       <c r="D447">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -11924,7 +11989,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>80074</t>
+          <t>80075</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -11933,7 +11998,7 @@
         </is>
       </c>
       <c r="D448">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -11949,7 +12014,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>80075</t>
+          <t>80076</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -11958,11 +12023,11 @@
         </is>
       </c>
       <c r="D449">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -11974,7 +12039,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>80076</t>
+          <t>80077</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -11983,11 +12048,11 @@
         </is>
       </c>
       <c r="D450">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -11999,7 +12064,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>80077</t>
+          <t>80078</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -12008,11 +12073,11 @@
         </is>
       </c>
       <c r="D451">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12089,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>80078</t>
+          <t>80079</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -12033,7 +12098,7 @@
         </is>
       </c>
       <c r="D452">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -12049,7 +12114,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -12058,11 +12123,11 @@
         </is>
       </c>
       <c r="D453">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12139,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>80081</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -12083,11 +12148,11 @@
         </is>
       </c>
       <c r="D454">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12099,20 +12164,25 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>90001</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D455">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -12124,20 +12194,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>90002</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D456">
-        <v>32</v>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>female</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -12154,12 +12216,20 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>90002</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="D457">
+        <v>25</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -12176,7 +12246,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>90004</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -12185,7 +12255,7 @@
         </is>
       </c>
       <c r="D458">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -12206,7 +12276,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>90004</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -12215,11 +12285,11 @@
         </is>
       </c>
       <c r="D459">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -12236,7 +12306,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>90005</t>
+          <t>90006</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -12245,11 +12315,11 @@
         </is>
       </c>
       <c r="D460">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -12266,7 +12336,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>90006</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -12275,11 +12345,11 @@
         </is>
       </c>
       <c r="D461">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -12296,7 +12366,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>90007</t>
+          <t>90008</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -12305,11 +12375,11 @@
         </is>
       </c>
       <c r="D462">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -12326,7 +12396,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>90008</t>
+          <t>90009</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -12335,7 +12405,7 @@
         </is>
       </c>
       <c r="D463">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -12356,7 +12426,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>90009</t>
+          <t>90010</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -12386,7 +12456,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>90010</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -12395,7 +12465,7 @@
         </is>
       </c>
       <c r="D465">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -12416,7 +12486,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>90011</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -12425,16 +12495,16 @@
         </is>
       </c>
       <c r="D466">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12516,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>90014</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -12455,7 +12525,7 @@
         </is>
       </c>
       <c r="D467">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -12476,7 +12546,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>90015</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -12485,11 +12555,11 @@
         </is>
       </c>
       <c r="D468">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -12506,7 +12576,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>90015</t>
+          <t>90016</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -12515,11 +12585,11 @@
         </is>
       </c>
       <c r="D469">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -12536,7 +12606,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>90016</t>
+          <t>90017</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -12545,11 +12615,11 @@
         </is>
       </c>
       <c r="D470">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -12566,7 +12636,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>90017</t>
+          <t>90018</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -12575,16 +12645,16 @@
         </is>
       </c>
       <c r="D471">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>HC</t>
+          <t>patient</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12666,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>90018</t>
+          <t>90019</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -12605,16 +12675,16 @@
         </is>
       </c>
       <c r="D472">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>patient</t>
+          <t>HC</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12696,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>90019</t>
+          <t>90020</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -12635,11 +12705,11 @@
         </is>
       </c>
       <c r="D473">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -12656,7 +12726,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>90020</t>
+          <t>90021</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -12665,11 +12735,11 @@
         </is>
       </c>
       <c r="D474">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -12686,7 +12756,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -12695,16 +12765,11 @@
         </is>
       </c>
       <c r="D475">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>female</t>
-        </is>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>HC</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12781,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>90022</t>
+          <t>90023</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -12725,7 +12790,7 @@
         </is>
       </c>
       <c r="D476">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -12741,7 +12806,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>90023</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -12750,11 +12815,11 @@
         </is>
       </c>
       <c r="D477">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12831,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>90025</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -12775,11 +12840,11 @@
         </is>
       </c>
       <c r="D478">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12856,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>90025</t>
+          <t>90027</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -12800,11 +12865,11 @@
         </is>
       </c>
       <c r="D479">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12881,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>90027</t>
+          <t>90028</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -12825,11 +12890,11 @@
         </is>
       </c>
       <c r="D480">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12906,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>90012</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -12849,39 +12914,39 @@
           <t>9</t>
         </is>
       </c>
-      <c r="D481">
-        <v>30</v>
-      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>female</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>patient</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>adults</t>
+          <t>adolescents</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>90012</t>
+          <t>70001</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D482">
+        <v>12</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>female</t>
-        </is>
-      </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>patient</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12958,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>70002</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -12902,7 +12967,7 @@
         </is>
       </c>
       <c r="D483">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -12918,7 +12983,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>70008</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -12927,7 +12992,7 @@
         </is>
       </c>
       <c r="D484">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -12943,7 +13008,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>70015</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -12952,7 +13017,7 @@
         </is>
       </c>
       <c r="D485">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -12968,7 +13033,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -12977,11 +13042,11 @@
         </is>
       </c>
       <c r="D486">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -12993,7 +13058,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>70017</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -13002,11 +13067,11 @@
         </is>
       </c>
       <c r="D487">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13083,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -13031,7 +13096,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13108,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>70023</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -13052,7 +13117,7 @@
         </is>
       </c>
       <c r="D489">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -13068,7 +13133,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>70026</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -13077,7 +13142,7 @@
         </is>
       </c>
       <c r="D490">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -13093,7 +13158,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>70027</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -13102,7 +13167,7 @@
         </is>
       </c>
       <c r="D491">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -13118,7 +13183,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13127,7 +13192,7 @@
         </is>
       </c>
       <c r="D492">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -13143,7 +13208,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70032</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13152,11 +13217,11 @@
         </is>
       </c>
       <c r="D493">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13233,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70033</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13177,7 +13242,7 @@
         </is>
       </c>
       <c r="D494">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -13193,7 +13258,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70034</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13218,7 +13283,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>70036</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13227,7 +13292,7 @@
         </is>
       </c>
       <c r="D496">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -13243,7 +13308,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70037</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13252,7 +13317,7 @@
         </is>
       </c>
       <c r="D497">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -13268,7 +13333,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13277,11 +13342,11 @@
         </is>
       </c>
       <c r="D498">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13293,7 +13358,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>70039</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13302,7 +13367,7 @@
         </is>
       </c>
       <c r="D499">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -13318,7 +13383,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13327,11 +13392,11 @@
         </is>
       </c>
       <c r="D500">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13408,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -13368,7 +13433,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>70044</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -13377,7 +13442,7 @@
         </is>
       </c>
       <c r="D502">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -13393,7 +13458,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -13402,11 +13467,11 @@
         </is>
       </c>
       <c r="D503">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13483,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -13427,11 +13492,11 @@
         </is>
       </c>
       <c r="D504">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13443,7 +13508,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70047</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -13456,7 +13521,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13468,7 +13533,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>70048</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -13493,7 +13558,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70050</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -13502,7 +13567,7 @@
         </is>
       </c>
       <c r="D507">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -13518,7 +13583,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>70051</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -13527,7 +13592,7 @@
         </is>
       </c>
       <c r="D508">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -13543,7 +13608,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -13556,7 +13621,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13568,7 +13633,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>70053</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -13581,7 +13646,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13658,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -13602,11 +13667,11 @@
         </is>
       </c>
       <c r="D511">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13683,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>70057</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -13627,11 +13692,11 @@
         </is>
       </c>
       <c r="D512">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13643,7 +13708,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>70058</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -13656,7 +13721,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13668,7 +13733,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>70062</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -13677,11 +13742,11 @@
         </is>
       </c>
       <c r="D514">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13693,7 +13758,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>70063</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -13718,7 +13783,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>70064</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -13727,7 +13792,7 @@
         </is>
       </c>
       <c r="D516">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -13743,7 +13808,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -13752,7 +13817,7 @@
         </is>
       </c>
       <c r="D517">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -13768,7 +13833,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>70066</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -13777,11 +13842,11 @@
         </is>
       </c>
       <c r="D518">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13858,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>70068</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -13818,7 +13883,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>70069</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -13827,11 +13892,11 @@
         </is>
       </c>
       <c r="D520">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13843,7 +13908,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>70070</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -13852,11 +13917,11 @@
         </is>
       </c>
       <c r="D521">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13933,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>70071</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -13877,7 +13942,7 @@
         </is>
       </c>
       <c r="D522">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -13893,7 +13958,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -13902,7 +13967,7 @@
         </is>
       </c>
       <c r="D523">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -13918,7 +13983,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -13927,7 +13992,7 @@
         </is>
       </c>
       <c r="D524">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -13943,7 +14008,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -13952,11 +14017,11 @@
         </is>
       </c>
       <c r="D525">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -13968,7 +14033,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>70075</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -13993,7 +14058,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>70076</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -14006,7 +14071,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14018,7 +14083,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -14027,11 +14092,11 @@
         </is>
       </c>
       <c r="D528">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14108,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14052,11 +14117,11 @@
         </is>
       </c>
       <c r="D529">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14133,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>70081</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14077,11 +14142,11 @@
         </is>
       </c>
       <c r="D530">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14093,7 +14158,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>70085</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -14118,7 +14183,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>70086</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -14127,11 +14192,11 @@
         </is>
       </c>
       <c r="D532">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14208,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>70087</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -14156,7 +14221,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14233,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>70088</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -14177,7 +14242,7 @@
         </is>
       </c>
       <c r="D534">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -14193,7 +14258,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>70089</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -14202,11 +14267,11 @@
         </is>
       </c>
       <c r="D535">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14218,7 +14283,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -14227,11 +14292,11 @@
         </is>
       </c>
       <c r="D536">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14308,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>70092</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -14252,11 +14317,11 @@
         </is>
       </c>
       <c r="D537">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14333,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14277,11 +14342,11 @@
         </is>
       </c>
       <c r="D538">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14358,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>70094</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -14302,11 +14367,11 @@
         </is>
       </c>
       <c r="D539">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14383,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -14331,7 +14396,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14408,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>70099</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -14356,7 +14421,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14368,7 +14433,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -14377,7 +14442,7 @@
         </is>
       </c>
       <c r="D542">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -14393,7 +14458,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>70102</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -14402,11 +14467,11 @@
         </is>
       </c>
       <c r="D543">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14418,7 +14483,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>70104</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -14443,7 +14508,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>70105</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -14452,11 +14517,11 @@
         </is>
       </c>
       <c r="D545">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14533,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>70106</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -14477,11 +14542,11 @@
         </is>
       </c>
       <c r="D546">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14558,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -14502,7 +14567,7 @@
         </is>
       </c>
       <c r="D547">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -14518,7 +14583,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>70108</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -14527,7 +14592,7 @@
         </is>
       </c>
       <c r="D548">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -14543,7 +14608,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -14552,11 +14617,11 @@
         </is>
       </c>
       <c r="D549">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14633,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>70110</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -14577,11 +14642,11 @@
         </is>
       </c>
       <c r="D550">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14658,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>70112</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -14602,11 +14667,11 @@
         </is>
       </c>
       <c r="D551">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14683,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -14627,7 +14692,7 @@
         </is>
       </c>
       <c r="D552">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -14643,7 +14708,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -14656,7 +14721,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14668,7 +14733,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>70115</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -14677,11 +14742,11 @@
         </is>
       </c>
       <c r="D554">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14693,7 +14758,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>70116</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -14702,7 +14767,7 @@
         </is>
       </c>
       <c r="D555">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -14718,7 +14783,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>70117</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -14727,11 +14792,11 @@
         </is>
       </c>
       <c r="D556">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14808,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -14756,7 +14821,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14833,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>70119</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -14777,7 +14842,7 @@
         </is>
       </c>
       <c r="D558">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -14793,7 +14858,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>70120</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -14804,11 +14869,6 @@
       <c r="D559">
         <v>17</v>
       </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -14818,7 +14878,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>70121</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -14827,7 +14887,12 @@
         </is>
       </c>
       <c r="D560">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="561">
@@ -14838,7 +14903,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>70122</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -14847,11 +14912,11 @@
         </is>
       </c>
       <c r="D561">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14928,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -14872,11 +14937,11 @@
         </is>
       </c>
       <c r="D562">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14953,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>70124</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -14897,7 +14962,7 @@
         </is>
       </c>
       <c r="D563">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
@@ -14913,7 +14978,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>70127</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -14922,11 +14987,11 @@
         </is>
       </c>
       <c r="D564">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -14938,7 +15003,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>70128</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -14947,11 +15012,11 @@
         </is>
       </c>
       <c r="D565">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -14963,7 +15028,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>70132</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -14988,7 +15053,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>70135</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -14997,11 +15062,11 @@
         </is>
       </c>
       <c r="D567">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15013,7 +15078,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>70136</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -15022,7 +15087,7 @@
         </is>
       </c>
       <c r="D568">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
@@ -15038,20 +15103,12 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>70138</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D569">
-        <v>15</v>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>female</t>
         </is>
       </c>
     </row>
@@ -15063,12 +15120,20 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>70140</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
           <t>7</t>
+        </is>
+      </c>
+      <c r="D570">
+        <v>14</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15145,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>70141</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -15089,7 +15154,7 @@
         </is>
       </c>
       <c r="D571">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
@@ -15105,7 +15170,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>70142</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15130,7 +15195,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15139,11 +15204,11 @@
         </is>
       </c>
       <c r="D573">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15220,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>70144</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15180,7 +15245,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>70145</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -15189,7 +15254,7 @@
         </is>
       </c>
       <c r="D575">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E575" t="inlineStr">
         <is>
@@ -15205,7 +15270,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>70146</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -15214,11 +15279,11 @@
         </is>
       </c>
       <c r="D576">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15295,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>70147</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -15239,11 +15304,11 @@
         </is>
       </c>
       <c r="D577">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15255,7 +15320,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>70148</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -15264,11 +15329,11 @@
         </is>
       </c>
       <c r="D578">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15345,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>70150</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -15289,7 +15354,7 @@
         </is>
       </c>
       <c r="D579">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E579" t="inlineStr">
         <is>
@@ -15305,7 +15370,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>70151</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -15330,7 +15395,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>70154</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -15339,11 +15404,11 @@
         </is>
       </c>
       <c r="D581">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15420,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>70155</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -15368,7 +15433,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15380,7 +15445,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>70157</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -15389,11 +15454,11 @@
         </is>
       </c>
       <c r="D583">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15405,7 +15470,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>70158</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -15414,7 +15479,7 @@
         </is>
       </c>
       <c r="D584">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E584" t="inlineStr">
         <is>
@@ -15430,7 +15495,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>70159</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -15439,11 +15504,11 @@
         </is>
       </c>
       <c r="D585">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15520,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>70160</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -15464,11 +15529,11 @@
         </is>
       </c>
       <c r="D586">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15545,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>70161</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -15489,7 +15554,7 @@
         </is>
       </c>
       <c r="D587">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
@@ -15505,7 +15570,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>70162</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -15514,12 +15579,7 @@
         </is>
       </c>
       <c r="D588">
-        <v>15</v>
-      </c>
-      <c r="E588" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="589">
@@ -15530,7 +15590,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>70163</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -15539,7 +15599,12 @@
         </is>
       </c>
       <c r="D589">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="590">
@@ -15550,7 +15615,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>70164</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -15559,11 +15624,11 @@
         </is>
       </c>
       <c r="D590">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15640,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -15584,7 +15649,7 @@
         </is>
       </c>
       <c r="D591">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
@@ -15600,7 +15665,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -15609,11 +15674,11 @@
         </is>
       </c>
       <c r="D592">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15690,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>70172</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -15650,7 +15715,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>70173</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -15659,11 +15724,11 @@
         </is>
       </c>
       <c r="D594">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15740,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>70174</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -15684,7 +15749,7 @@
         </is>
       </c>
       <c r="D595">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
@@ -15700,7 +15765,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>70175</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -15709,7 +15774,7 @@
         </is>
       </c>
       <c r="D596">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
@@ -15725,7 +15790,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>70176</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -15734,7 +15799,7 @@
         </is>
       </c>
       <c r="D597">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E597" t="inlineStr">
         <is>
@@ -15750,7 +15815,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -15759,11 +15824,11 @@
         </is>
       </c>
       <c r="D598">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15840,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -15800,7 +15865,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -15811,11 +15876,6 @@
       <c r="D600">
         <v>16</v>
       </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -15825,7 +15885,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -15834,7 +15894,12 @@
         </is>
       </c>
       <c r="D601">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
     </row>
     <row r="602">
@@ -15845,7 +15910,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>70182</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -15854,7 +15919,7 @@
         </is>
       </c>
       <c r="D602">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E602" t="inlineStr">
         <is>
@@ -15870,7 +15935,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>70184</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -15895,7 +15960,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>70185</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -15920,7 +15985,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -15929,12 +15994,7 @@
         </is>
       </c>
       <c r="D605">
-        <v>16</v>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>17</v>
       </c>
     </row>
     <row r="606">
@@ -15945,7 +16005,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>70188</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -15954,7 +16014,12 @@
         </is>
       </c>
       <c r="D606">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
     </row>
     <row r="607">
@@ -15965,7 +16030,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>70193</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -15974,11 +16039,11 @@
         </is>
       </c>
       <c r="D607">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -15990,7 +16055,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -15999,11 +16064,11 @@
         </is>
       </c>
       <c r="D608">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16080,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>70196</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16040,7 +16105,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -16049,11 +16114,11 @@
         </is>
       </c>
       <c r="D610">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16130,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>70199</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -16074,7 +16139,7 @@
         </is>
       </c>
       <c r="D611">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E611" t="inlineStr">
         <is>
@@ -16090,7 +16155,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>70200</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -16099,7 +16164,7 @@
         </is>
       </c>
       <c r="D612">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
@@ -16115,7 +16180,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16128,7 +16193,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
     </row>
@@ -16140,20 +16205,12 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D614">
-        <v>17</v>
-      </c>
-      <c r="E614" t="inlineStr">
-        <is>
-          <t>male</t>
         </is>
       </c>
     </row>
@@ -16165,7 +16222,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>70090</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16173,27 +16230,10 @@
           <t>7</t>
         </is>
       </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>adolescents</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D616">
+      <c r="D615">
         <v>16</v>
       </c>
-      <c r="E616" t="inlineStr">
+      <c r="E615" t="inlineStr">
         <is>
           <t>female</t>
         </is>
